--- a/SGC-CKN/Excel/t9fwaf_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
+++ b/SGC-CKN/Excel/t9fwaf_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
@@ -47,7 +47,7 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>D2000</t>
+    <t>D1000</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>

--- a/SGC-CKN/Excel/t9fwaf_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
+++ b/SGC-CKN/Excel/t9fwaf_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
@@ -47,7 +47,7 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>D1000</t>
+    <t>D100</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>
